--- a/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G2" t="n">
-        <v>1.636806077445916</v>
+        <v>1.610196974376472</v>
       </c>
       <c r="H2" t="n">
-        <v>3.857825468251492</v>
+        <v>3.864609487768953</v>
       </c>
       <c r="I2" t="n">
         <v>-10.29308361861639</v>
@@ -545,16 +545,16 @@
         <v>17.42999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>34.25414364640884</v>
+        <v>34.375</v>
       </c>
       <c r="L2" t="n">
         <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>9.789473684210526</v>
+        <v>9.842105263157896</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1730179568495224</v>
+        <v>0.1711356954525501</v>
       </c>
       <c r="O2" t="n">
         <v>0.01526130786432289</v>
@@ -603,7 +603,7 @@
         <v>16.16500377295211</v>
       </c>
       <c r="K3" t="n">
-        <v>16.57458563535911</v>
+        <v>16.54411764705882</v>
       </c>
       <c r="L3" t="n">
         <v>18</v>
@@ -661,7 +661,7 @@
         <v>8.523157098428168</v>
       </c>
       <c r="K4" t="n">
-        <v>19.70534069981584</v>
+        <v>19.66911764705882</v>
       </c>
       <c r="L4" t="n">
         <v>18</v>
@@ -719,7 +719,7 @@
         <v>12.5359029000278</v>
       </c>
       <c r="K5" t="n">
-        <v>29.46593001841621</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G6" t="n">
-        <v>1.377388240398188</v>
+        <v>1.319153660793221</v>
       </c>
       <c r="H6" t="n">
-        <v>4.305733957927844</v>
+        <v>4.326921994965913</v>
       </c>
       <c r="I6" t="n">
         <v>-8.97730231120652</v>
@@ -777,16 +777,16 @@
         <v>16.1167748089563</v>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L6" t="n">
         <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1259193300496518</v>
+        <v>0.1215792248538132</v>
       </c>
       <c r="O6" t="n">
         <v>-0.09264081476093833</v>
@@ -835,7 +835,7 @@
         <v>11.7821325405861</v>
       </c>
       <c r="K7" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -893,7 +893,7 @@
         <v>8.157897599276009</v>
       </c>
       <c r="K8" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
@@ -951,7 +951,7 @@
         <v>13.6888940729176</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L9" t="n">
         <v>12</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1.272571541698505</v>
+        <v>1.131681703508261</v>
       </c>
       <c r="H10" t="n">
-        <v>3.992142625541164</v>
+        <v>4.011759388551176</v>
       </c>
       <c r="I10" t="n">
         <v>-4.724652064266159</v>
@@ -1009,19 +1009,19 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K10" t="n">
-        <v>41.02564102564102</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>10.66666666666667</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1399415553099277</v>
+        <v>0.1279569235329006</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06473491471119242</v>
+        <v>0.02878101938011102</v>
       </c>
       <c r="P10" t="n">
         <v>0.2858220548416497</v>
@@ -1067,7 +1067,7 @@
         <v>7.09284827773554</v>
       </c>
       <c r="K11" t="n">
-        <v>8.974358974358974</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
@@ -1125,7 +1125,7 @@
         <v>7.65174934622371</v>
       </c>
       <c r="K12" t="n">
-        <v>6.41025641025641</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K13" t="n">
-        <v>43.58974358974359</v>
+        <v>43.03797468354431</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" t="n">
-        <v>1.341626167319033</v>
+        <v>1.270574841494515</v>
       </c>
       <c r="H14" t="n">
-        <v>4.240221503288286</v>
+        <v>4.282915374474388</v>
       </c>
       <c r="I14" t="n">
         <v>-7.39121056995352</v>
@@ -1241,16 +1241,16 @@
         <v>10.5507582207258</v>
       </c>
       <c r="K14" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L14" t="n">
         <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1243365743757262</v>
+        <v>0.1183132423867887</v>
       </c>
       <c r="O14" t="n">
         <v>-0.1107307878394987</v>
@@ -1299,7 +1299,7 @@
         <v>14.9951975592301</v>
       </c>
       <c r="K15" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L15" t="n">
         <v>12</v>
@@ -1357,7 +1357,7 @@
         <v>12.0388754904431</v>
       </c>
       <c r="K16" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
         <v>17.0568622218592</v>
       </c>
       <c r="K17" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L17" t="n">
         <v>12</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9747101032362862</v>
+        <v>0.9524007134020059</v>
       </c>
       <c r="H18" t="n">
-        <v>3.540214091248604</v>
+        <v>3.530794520340923</v>
       </c>
       <c r="I18" t="n">
         <v>-9.00069743294255</v>
@@ -1473,16 +1473,16 @@
         <v>9.585535370371879</v>
       </c>
       <c r="K18" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L18" t="n">
         <v>12</v>
       </c>
       <c r="M18" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>0.08620963184928609</v>
+        <v>0.08505448072170881</v>
       </c>
       <c r="O18" t="n">
         <v>-0.06249589774862385</v>
@@ -1531,7 +1531,7 @@
         <v>10.6235569673087</v>
       </c>
       <c r="K19" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
@@ -1589,7 +1589,7 @@
         <v>11.9143823646577</v>
       </c>
       <c r="K20" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
         <v>6.793266873392841</v>
       </c>
       <c r="K21" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L21" t="n">
         <v>12</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8551892799233083</v>
+        <v>0.8190472649359588</v>
       </c>
       <c r="H22" t="n">
-        <v>5.185150853555981</v>
+        <v>5.173799013631518</v>
       </c>
       <c r="I22" t="n">
         <v>-10.7369500066555</v>
@@ -1705,19 +1705,19 @@
         <v>28.2407194114024</v>
       </c>
       <c r="K22" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L22" t="n">
         <v>12</v>
       </c>
       <c r="M22" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07787199527246416</v>
+        <v>0.07594795450451906</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2241417343000396</v>
+        <v>-0.2472302235153808</v>
       </c>
       <c r="P22" t="n">
         <v>0.3961971237699671</v>
@@ -1763,7 +1763,7 @@
         <v>10.1238105397411</v>
       </c>
       <c r="K23" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L23" t="n">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>13.2720975781699</v>
       </c>
       <c r="K24" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>25.211119079268</v>
       </c>
       <c r="K25" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L25" t="n">
         <v>12</v>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G26" t="n">
-        <v>1.837052601249605</v>
+        <v>1.782554453281759</v>
       </c>
       <c r="H26" t="n">
-        <v>4.097069879777519</v>
+        <v>4.115937342858582</v>
       </c>
       <c r="I26" t="n">
         <v>-9.635645143182661</v>
@@ -1937,16 +1937,16 @@
         <v>16.1158229524901</v>
       </c>
       <c r="K26" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L26" t="n">
         <v>12</v>
       </c>
       <c r="M26" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1724670162504804</v>
+        <v>0.1683955094476174</v>
       </c>
       <c r="O26" t="n">
         <v>-0.02947196847005373</v>
@@ -1995,7 +1995,7 @@
         <v>9.768282119936639</v>
       </c>
       <c r="K27" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L27" t="n">
         <v>12</v>
@@ -2053,7 +2053,7 @@
         <v>8.49076575066875</v>
       </c>
       <c r="K28" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>12.07642730623</v>
       </c>
       <c r="K29" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L29" t="n">
         <v>12</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G30" t="n">
-        <v>1.096899533468198</v>
+        <v>1.042242572213268</v>
       </c>
       <c r="H30" t="n">
-        <v>3.991148814057161</v>
+        <v>4.011760732565727</v>
       </c>
       <c r="I30" t="n">
         <v>-10.8112251477361</v>
@@ -2169,16 +2169,16 @@
         <v>9.39119756344274</v>
       </c>
       <c r="K30" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L30" t="n">
         <v>12</v>
       </c>
       <c r="M30" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1045253757856958</v>
+        <v>0.1008290260566785</v>
       </c>
       <c r="O30" t="n">
         <v>-0.2594245775460494</v>
@@ -2227,7 +2227,7 @@
         <v>10.5168773145652</v>
       </c>
       <c r="K31" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L31" t="n">
         <v>12</v>
@@ -2285,7 +2285,7 @@
         <v>12.0090481450406</v>
       </c>
       <c r="K32" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>20.1357853233765</v>
       </c>
       <c r="K33" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L33" t="n">
         <v>12</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G34" t="n">
-        <v>1.273943101733727</v>
+        <v>1.242362749611182</v>
       </c>
       <c r="H34" t="n">
-        <v>3.905770061085678</v>
+        <v>3.900701148881366</v>
       </c>
       <c r="I34" t="n">
         <v>-11.3876720879084</v>
@@ -2401,16 +2401,16 @@
         <v>12.109209792019</v>
       </c>
       <c r="K34" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L34" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1168966052414636</v>
+        <v>0.1148552863681656</v>
       </c>
       <c r="O34" t="n">
         <v>-0.08087269380805873</v>
@@ -2459,7 +2459,7 @@
         <v>8.0175198917632</v>
       </c>
       <c r="K35" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L35" t="n">
         <v>12</v>
@@ -2517,7 +2517,7 @@
         <v>8.33833543505675</v>
       </c>
       <c r="K36" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L36" t="n">
         <v>10</v>
@@ -2575,7 +2575,7 @@
         <v>15.3362226075419</v>
       </c>
       <c r="K37" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L37" t="n">
         <v>12</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G38" t="n">
-        <v>1.375068516377407</v>
+        <v>1.27610153566427</v>
       </c>
       <c r="H38" t="n">
-        <v>5.950223897882283</v>
+        <v>6.008842276135086</v>
       </c>
       <c r="I38" t="n">
         <v>-12.2948760443384</v>
@@ -2633,16 +2633,16 @@
         <v>19.7034328806292</v>
       </c>
       <c r="K38" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L38" t="n">
         <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1255944303304871</v>
+        <v>0.1164458417716525</v>
       </c>
       <c r="O38" t="n">
         <v>-0.2342435165396028</v>
@@ -2691,7 +2691,7 @@
         <v>15.3631100623459</v>
       </c>
       <c r="K39" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -2749,7 +2749,7 @@
         <v>21.9468390804598</v>
       </c>
       <c r="K40" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L40" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>29.6127554257064</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L41" t="n">
         <v>12</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G42" t="n">
-        <v>1.631953697597222</v>
+        <v>1.615308826197647</v>
       </c>
       <c r="H42" t="n">
-        <v>5.007471232994456</v>
+        <v>4.986514646365134</v>
       </c>
       <c r="I42" t="n">
         <v>-10.9393768664177</v>
@@ -2865,19 +2865,19 @@
         <v>14.5795620340833</v>
       </c>
       <c r="K42" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L42" t="n">
         <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1508575647433518</v>
+        <v>0.1507567468514205</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.08626110315509194</v>
+        <v>-0.08747091785826677</v>
       </c>
       <c r="P42" t="n">
         <v>0.4668459700393814</v>
@@ -2923,7 +2923,7 @@
         <v>10.463139776602</v>
       </c>
       <c r="K43" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L43" t="n">
         <v>12</v>
@@ -2981,7 +2981,7 @@
         <v>11.502191267126</v>
       </c>
       <c r="K44" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L44" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K45" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L45" t="n">
         <v>12</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G46" t="n">
-        <v>1.292707877841557</v>
+        <v>1.135479736112159</v>
       </c>
       <c r="H46" t="n">
-        <v>4.720673415920713</v>
+        <v>4.760506629179263</v>
       </c>
       <c r="I46" t="n">
         <v>-7.641550815508549</v>
@@ -3097,19 +3097,19 @@
         <v>13.2283841318109</v>
       </c>
       <c r="K46" t="n">
-        <v>37.62376237623762</v>
+        <v>38.23529411764706</v>
       </c>
       <c r="L46" t="n">
         <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1238193323787008</v>
+        <v>0.1109077722028314</v>
       </c>
       <c r="O46" t="n">
-        <v>0.01998150231082008</v>
+        <v>0.01560353545881421</v>
       </c>
       <c r="P46" t="n">
         <v>0.3138540007036315</v>
@@ -3155,7 +3155,7 @@
         <v>11.9534070082495</v>
       </c>
       <c r="K47" t="n">
-        <v>12.87128712871287</v>
+        <v>12.74509803921569</v>
       </c>
       <c r="L47" t="n">
         <v>6</v>
@@ -3213,7 +3213,7 @@
         <v>5.99996918574318</v>
       </c>
       <c r="K48" t="n">
-        <v>4.95049504950495</v>
+        <v>4.901960784313726</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3271,7 +3271,7 @@
         <v>14.1184473609332</v>
       </c>
       <c r="K49" t="n">
-        <v>44.55445544554455</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="L49" t="n">
         <v>5</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7730859255370722</v>
+        <v>0.7339361232340852</v>
       </c>
       <c r="H50" t="n">
-        <v>4.048888581993833</v>
+        <v>4.049671237772323</v>
       </c>
       <c r="I50" t="n">
         <v>-9.48046022451167</v>
@@ -3329,16 +3329,16 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K50" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L50" t="n">
         <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0697475614354426</v>
+        <v>0.06675140349118582</v>
       </c>
       <c r="O50" t="n">
         <v>-0.1552012693445518</v>
@@ -3387,7 +3387,7 @@
         <v>13.0214086312522</v>
       </c>
       <c r="K51" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L51" t="n">
         <v>12</v>
@@ -3445,7 +3445,7 @@
         <v>12.2238347773583</v>
       </c>
       <c r="K52" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L52" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L53" t="n">
         <v>12</v>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7295896495725761</v>
+        <v>0.7370605764745146</v>
       </c>
       <c r="H54" t="n">
-        <v>3.659178140343884</v>
+        <v>3.642524011205614</v>
       </c>
       <c r="I54" t="n">
         <v>-8.016951710911901</v>
@@ -3561,16 +3561,16 @@
         <v>9.074501372422739</v>
       </c>
       <c r="K54" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L54" t="n">
         <v>12</v>
       </c>
       <c r="M54" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0697568214383283</v>
+        <v>0.0713024323974092</v>
       </c>
       <c r="O54" t="n">
         <v>-0.184079252512853</v>
@@ -3619,7 +3619,7 @@
         <v>8.09206131391011</v>
       </c>
       <c r="K55" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L55" t="n">
         <v>12</v>
@@ -3677,7 +3677,7 @@
         <v>6.97269921720136</v>
       </c>
       <c r="K56" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L56" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
         <v>20.8483922702477</v>
       </c>
       <c r="K57" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L57" t="n">
         <v>12</v>

--- a/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G2" t="n">
-        <v>1.610196974376472</v>
+        <v>1.66085423558476</v>
       </c>
       <c r="H2" t="n">
-        <v>3.864609487768953</v>
+        <v>3.844303865270501</v>
       </c>
       <c r="I2" t="n">
         <v>-10.29308361861639</v>
@@ -545,16 +545,16 @@
         <v>17.42999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>34.375</v>
+        <v>34.4954128440367</v>
       </c>
       <c r="L2" t="n">
         <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>9.842105263157896</v>
+        <v>9.894736842105264</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1711356954525501</v>
+        <v>0.1774969569522575</v>
       </c>
       <c r="O2" t="n">
         <v>0.01526130786432289</v>
@@ -603,7 +603,7 @@
         <v>16.16500377295211</v>
       </c>
       <c r="K3" t="n">
-        <v>16.54411764705882</v>
+        <v>16.51376146788991</v>
       </c>
       <c r="L3" t="n">
         <v>18</v>
@@ -661,7 +661,7 @@
         <v>8.523157098428168</v>
       </c>
       <c r="K4" t="n">
-        <v>19.66911764705882</v>
+        <v>19.63302752293578</v>
       </c>
       <c r="L4" t="n">
         <v>18</v>
@@ -719,7 +719,7 @@
         <v>12.5359029000278</v>
       </c>
       <c r="K5" t="n">
-        <v>29.41176470588236</v>
+        <v>29.35779816513762</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G6" t="n">
-        <v>1.319153660793221</v>
+        <v>1.456502723589905</v>
       </c>
       <c r="H6" t="n">
-        <v>4.326921994965913</v>
+        <v>4.304656609520738</v>
       </c>
       <c r="I6" t="n">
         <v>-8.97730231120652</v>
@@ -777,16 +777,16 @@
         <v>16.1167748089563</v>
       </c>
       <c r="K6" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L6" t="n">
         <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1215792248538132</v>
+        <v>0.1363545240636568</v>
       </c>
       <c r="O6" t="n">
         <v>-0.09264081476093833</v>
@@ -835,7 +835,7 @@
         <v>11.7821325405861</v>
       </c>
       <c r="K7" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -893,7 +893,7 @@
         <v>8.157897599276009</v>
       </c>
       <c r="K8" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
@@ -951,7 +951,7 @@
         <v>13.6888940729176</v>
       </c>
       <c r="K9" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L9" t="n">
         <v>12</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>1.131681703508261</v>
+        <v>1.545367764507353</v>
       </c>
       <c r="H10" t="n">
-        <v>4.011759388551176</v>
+        <v>4.026401837250746</v>
       </c>
       <c r="I10" t="n">
         <v>-4.724652064266159</v>
@@ -1009,19 +1009,19 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K10" t="n">
-        <v>41.77215189873418</v>
+        <v>42.5</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1279569235329006</v>
+        <v>0.1831244553352133</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02878101938011102</v>
+        <v>0.06926769637694097</v>
       </c>
       <c r="P10" t="n">
         <v>0.2858220548416497</v>
@@ -1067,7 +1067,7 @@
         <v>7.09284827773554</v>
       </c>
       <c r="K11" t="n">
-        <v>8.860759493670885</v>
+        <v>8.75</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
@@ -1125,7 +1125,7 @@
         <v>7.65174934622371</v>
       </c>
       <c r="K12" t="n">
-        <v>6.329113924050633</v>
+        <v>6.25</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K13" t="n">
-        <v>43.03797468354431</v>
+        <v>42.5</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G14" t="n">
-        <v>1.270574841494515</v>
+        <v>1.391037311042302</v>
       </c>
       <c r="H14" t="n">
-        <v>4.282915374474388</v>
+        <v>4.223450032974992</v>
       </c>
       <c r="I14" t="n">
         <v>-7.39121056995352</v>
@@ -1241,16 +1241,16 @@
         <v>10.5507582207258</v>
       </c>
       <c r="K14" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L14" t="n">
         <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1183132423867887</v>
+        <v>0.1322119707335318</v>
       </c>
       <c r="O14" t="n">
         <v>-0.1107307878394987</v>
@@ -1299,7 +1299,7 @@
         <v>14.9951975592301</v>
       </c>
       <c r="K15" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L15" t="n">
         <v>12</v>
@@ -1357,7 +1357,7 @@
         <v>12.0388754904431</v>
       </c>
       <c r="K16" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
         <v>17.0568622218592</v>
       </c>
       <c r="K17" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L17" t="n">
         <v>12</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9524007134020059</v>
+        <v>1.014935391327171</v>
       </c>
       <c r="H18" t="n">
-        <v>3.530794520340923</v>
+        <v>3.528539640680341</v>
       </c>
       <c r="I18" t="n">
         <v>-9.00069743294255</v>
@@ -1473,16 +1473,16 @@
         <v>9.585535370371879</v>
       </c>
       <c r="K18" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L18" t="n">
         <v>12</v>
       </c>
       <c r="M18" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N18" t="n">
-        <v>0.08505448072170881</v>
+        <v>0.09145747466591085</v>
       </c>
       <c r="O18" t="n">
         <v>-0.06249589774862385</v>
@@ -1531,7 +1531,7 @@
         <v>10.6235569673087</v>
       </c>
       <c r="K19" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
@@ -1589,7 +1589,7 @@
         <v>11.9143823646577</v>
       </c>
       <c r="K20" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
         <v>6.793266873392841</v>
       </c>
       <c r="K21" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L21" t="n">
         <v>12</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8190472649359588</v>
+        <v>0.8500926746393325</v>
       </c>
       <c r="H22" t="n">
-        <v>5.173799013631518</v>
+        <v>5.255273811216077</v>
       </c>
       <c r="I22" t="n">
         <v>-10.7369500066555</v>
@@ -1705,19 +1705,19 @@
         <v>28.2407194114024</v>
       </c>
       <c r="K22" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L22" t="n">
         <v>12</v>
       </c>
       <c r="M22" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07594795450451906</v>
+        <v>0.07820321347097516</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2472302235153808</v>
+        <v>-0.2201671159179077</v>
       </c>
       <c r="P22" t="n">
         <v>0.3961971237699671</v>
@@ -1763,7 +1763,7 @@
         <v>10.1238105397411</v>
       </c>
       <c r="K23" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L23" t="n">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>13.2720975781699</v>
       </c>
       <c r="K24" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>25.211119079268</v>
       </c>
       <c r="K25" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L25" t="n">
         <v>12</v>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G26" t="n">
-        <v>1.782554453281759</v>
+        <v>1.902253453996314</v>
       </c>
       <c r="H26" t="n">
-        <v>4.115937342858582</v>
+        <v>4.086037239915052</v>
       </c>
       <c r="I26" t="n">
         <v>-9.635645143182661</v>
@@ -1937,16 +1937,16 @@
         <v>16.1158229524901</v>
       </c>
       <c r="K26" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L26" t="n">
         <v>12</v>
       </c>
       <c r="M26" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1683955094476174</v>
+        <v>0.1837662420049963</v>
       </c>
       <c r="O26" t="n">
         <v>-0.02947196847005373</v>
@@ -1995,7 +1995,7 @@
         <v>9.768282119936639</v>
       </c>
       <c r="K27" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L27" t="n">
         <v>12</v>
@@ -2053,7 +2053,7 @@
         <v>8.49076575066875</v>
       </c>
       <c r="K28" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>12.07642730623</v>
       </c>
       <c r="K29" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L29" t="n">
         <v>12</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G30" t="n">
-        <v>1.042242572213268</v>
+        <v>1.109061151587155</v>
       </c>
       <c r="H30" t="n">
-        <v>4.011760732565727</v>
+        <v>3.954557161787932</v>
       </c>
       <c r="I30" t="n">
         <v>-10.8112251477361</v>
@@ -2169,16 +2169,16 @@
         <v>9.39119756344274</v>
       </c>
       <c r="K30" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L30" t="n">
         <v>12</v>
       </c>
       <c r="M30" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1008290260566785</v>
+        <v>0.1072992395182234</v>
       </c>
       <c r="O30" t="n">
         <v>-0.2594245775460494</v>
@@ -2227,7 +2227,7 @@
         <v>10.5168773145652</v>
       </c>
       <c r="K31" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L31" t="n">
         <v>12</v>
@@ -2285,7 +2285,7 @@
         <v>12.0090481450406</v>
       </c>
       <c r="K32" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>20.1357853233765</v>
       </c>
       <c r="K33" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L33" t="n">
         <v>12</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G34" t="n">
-        <v>1.242362749611182</v>
+        <v>1.316453063907418</v>
       </c>
       <c r="H34" t="n">
-        <v>3.900701148881366</v>
+        <v>3.882940192696579</v>
       </c>
       <c r="I34" t="n">
         <v>-11.3876720879084</v>
@@ -2401,16 +2401,16 @@
         <v>12.109209792019</v>
       </c>
       <c r="K34" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L34" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1148552863681656</v>
+        <v>0.1239991756367903</v>
       </c>
       <c r="O34" t="n">
         <v>-0.08087269380805873</v>
@@ -2459,7 +2459,7 @@
         <v>8.0175198917632</v>
       </c>
       <c r="K35" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L35" t="n">
         <v>12</v>
@@ -2517,7 +2517,7 @@
         <v>8.33833543505675</v>
       </c>
       <c r="K36" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L36" t="n">
         <v>10</v>
@@ -2575,7 +2575,7 @@
         <v>15.3362226075419</v>
       </c>
       <c r="K37" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L37" t="n">
         <v>12</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G38" t="n">
-        <v>1.27610153566427</v>
+        <v>1.583862459137402</v>
       </c>
       <c r="H38" t="n">
-        <v>6.008842276135086</v>
+        <v>6.147623011817134</v>
       </c>
       <c r="I38" t="n">
         <v>-12.2948760443384</v>
@@ -2633,22 +2633,22 @@
         <v>19.7034328806292</v>
       </c>
       <c r="K38" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L38" t="n">
         <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1164458417716525</v>
+        <v>0.1519597065963022</v>
       </c>
       <c r="O38" t="n">
         <v>-0.2342435165396028</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4703989394914552</v>
+        <v>0.5207482806671548</v>
       </c>
     </row>
     <row r="39">
@@ -2691,7 +2691,7 @@
         <v>15.3631100623459</v>
       </c>
       <c r="K39" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -2749,7 +2749,7 @@
         <v>21.9468390804598</v>
       </c>
       <c r="K40" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L40" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>29.6127554257064</v>
       </c>
       <c r="K41" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L41" t="n">
         <v>12</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G42" t="n">
-        <v>1.615308826197647</v>
+        <v>1.626866338579104</v>
       </c>
       <c r="H42" t="n">
-        <v>4.986514646365134</v>
+        <v>4.96098088233609</v>
       </c>
       <c r="I42" t="n">
         <v>-10.9393768664177</v>
@@ -2865,19 +2865,19 @@
         <v>14.5795620340833</v>
       </c>
       <c r="K42" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L42" t="n">
         <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1507567468514205</v>
+        <v>0.1529391006137088</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.08747091785826677</v>
+        <v>-0.06815823317850678</v>
       </c>
       <c r="P42" t="n">
         <v>0.4668459700393814</v>
@@ -2923,7 +2923,7 @@
         <v>10.463139776602</v>
       </c>
       <c r="K43" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L43" t="n">
         <v>12</v>
@@ -2981,7 +2981,7 @@
         <v>11.502191267126</v>
       </c>
       <c r="K44" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L44" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K45" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L45" t="n">
         <v>12</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G46" t="n">
-        <v>1.135479736112159</v>
+        <v>1.500067138249088</v>
       </c>
       <c r="H46" t="n">
-        <v>4.760506629179263</v>
+        <v>4.689188130623344</v>
       </c>
       <c r="I46" t="n">
         <v>-7.641550815508549</v>
@@ -3097,19 +3097,19 @@
         <v>13.2283841318109</v>
       </c>
       <c r="K46" t="n">
-        <v>38.23529411764706</v>
+        <v>38.83495145631068</v>
       </c>
       <c r="L46" t="n">
         <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1109077722028314</v>
+        <v>0.1536330293644707</v>
       </c>
       <c r="O46" t="n">
-        <v>0.01560353545881421</v>
+        <v>0.01998150231082008</v>
       </c>
       <c r="P46" t="n">
         <v>0.3138540007036315</v>
@@ -3155,7 +3155,7 @@
         <v>11.9534070082495</v>
       </c>
       <c r="K47" t="n">
-        <v>12.74509803921569</v>
+        <v>12.62135922330097</v>
       </c>
       <c r="L47" t="n">
         <v>6</v>
@@ -3213,7 +3213,7 @@
         <v>5.99996918574318</v>
       </c>
       <c r="K48" t="n">
-        <v>4.901960784313726</v>
+        <v>4.854368932038835</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3271,7 +3271,7 @@
         <v>14.1184473609332</v>
       </c>
       <c r="K49" t="n">
-        <v>44.11764705882353</v>
+        <v>43.68932038834951</v>
       </c>
       <c r="L49" t="n">
         <v>5</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7339361232340852</v>
+        <v>0.8691050171989759</v>
       </c>
       <c r="H50" t="n">
-        <v>4.049671237772323</v>
+        <v>4.071497655130523</v>
       </c>
       <c r="I50" t="n">
         <v>-9.48046022451167</v>
@@ -3329,16 +3329,16 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K50" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L50" t="n">
         <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N50" t="n">
-        <v>0.06675140349118582</v>
+        <v>0.08054328644176401</v>
       </c>
       <c r="O50" t="n">
         <v>-0.1552012693445518</v>
@@ -3387,7 +3387,7 @@
         <v>13.0214086312522</v>
       </c>
       <c r="K51" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L51" t="n">
         <v>12</v>
@@ -3445,7 +3445,7 @@
         <v>12.2238347773583</v>
       </c>
       <c r="K52" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L52" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K53" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L53" t="n">
         <v>12</v>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7370605764745146</v>
+        <v>0.7368961166608688</v>
       </c>
       <c r="H54" t="n">
-        <v>3.642524011205614</v>
+        <v>3.626588581944838</v>
       </c>
       <c r="I54" t="n">
         <v>-8.016951710911901</v>
@@ -3561,16 +3561,16 @@
         <v>9.074501372422739</v>
       </c>
       <c r="K54" t="n">
-        <v>35.21594684385382</v>
+        <v>35.43046357615894</v>
       </c>
       <c r="L54" t="n">
         <v>12</v>
       </c>
       <c r="M54" t="n">
-        <v>8.833333333333334</v>
+        <v>8.916666666666666</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0713024323974092</v>
+        <v>0.07203938989856955</v>
       </c>
       <c r="O54" t="n">
         <v>-0.184079252512853</v>
@@ -3619,7 +3619,7 @@
         <v>8.09206131391011</v>
       </c>
       <c r="K55" t="n">
-        <v>14.28571428571428</v>
+        <v>14.23841059602649</v>
       </c>
       <c r="L55" t="n">
         <v>12</v>
@@ -3677,7 +3677,7 @@
         <v>6.97269921720136</v>
       </c>
       <c r="K56" t="n">
-        <v>19.60132890365449</v>
+        <v>19.5364238410596</v>
       </c>
       <c r="L56" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
         <v>20.8483922702477</v>
       </c>
       <c r="K57" t="n">
-        <v>30.89700996677741</v>
+        <v>30.79470198675497</v>
       </c>
       <c r="L57" t="n">
         <v>12</v>
@@ -3751,9 +3751,1224 @@
       </c>
       <c r="P57" t="n">
         <v>0.4382771903522265</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Australian_Fixed_Interest</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>168</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.5764270921737074</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.181667925920913</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-3.5808884985017</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.503733642227802</v>
+      </c>
+      <c r="K58" t="n">
+        <v>39.34426229508197</v>
+      </c>
+      <c r="L58" t="n">
+        <v>15</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.07166159676513875</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-0.0120745479938501</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.5031331879659144</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Australian_Fixed_Interest</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>59</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.4884921770248766</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.105096012266704</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-1.631712530342599</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.402309746334153</v>
+      </c>
+      <c r="K59" t="n">
+        <v>13.81733021077283</v>
+      </c>
+      <c r="L59" t="n">
+        <v>14</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4.214285714285714</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.02063592154328637</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-0.01379060489315265</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.05241297425934888</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Australian_Fixed_Interest</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>74</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.5843328880085029</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.105738748289514</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-2.515642872592327</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4.116485870291786</v>
+      </c>
+      <c r="K60" t="n">
+        <v>17.33021077283372</v>
+      </c>
+      <c r="L60" t="n">
+        <v>14</v>
+      </c>
+      <c r="M60" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.03150046006894134</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-0.01520952015229449</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.1061817635984028</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Australian_Fixed_Interest</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>126</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.5416499986939293</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.335246697321326</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-3.747483162187848</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4.260323410130962</v>
+      </c>
+      <c r="K61" t="n">
+        <v>29.50819672131147</v>
+      </c>
+      <c r="L61" t="n">
+        <v>14</v>
+      </c>
+      <c r="M61" t="n">
+        <v>9</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.05194384465463737</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-0.09935519460501041</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.210471468967329</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Australian_Government_Bonds</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>176</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.5318193736509128</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.314382132344291</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-4.206622271745363</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.744396140912065</v>
+      </c>
+      <c r="K62" t="n">
+        <v>39.46188340807175</v>
+      </c>
+      <c r="L62" t="n">
+        <v>16</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.06450120300299837</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-0.02204332401546116</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.4803096162708709</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Australian_Government_Bonds</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>59</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.4730525871391192</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.204336584950799</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-1.788532334754889</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.553979827111342</v>
+      </c>
+      <c r="K63" t="n">
+        <v>13.22869955156951</v>
+      </c>
+      <c r="L63" t="n">
+        <v>14</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4.214285714285714</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.01992410381680362</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-0.0174137605619753</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.05058286542926149</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Australian_Government_Bonds</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>85</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.6033313082371834</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.234850904718243</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-2.7242514498934</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4.289426931116491</v>
+      </c>
+      <c r="K64" t="n">
+        <v>19.05829596412556</v>
+      </c>
+      <c r="L64" t="n">
+        <v>14</v>
+      </c>
+      <c r="M64" t="n">
+        <v>6.071428571428571</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.03753120914407915</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-0.01780322281401037</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.1133423661045854</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Australian_Government_Bonds</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>126</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5426439894064998</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.494990032714351</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-4.025340327634774</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.441637267010878</v>
+      </c>
+      <c r="K65" t="n">
+        <v>28.25112107623318</v>
+      </c>
+      <c r="L65" t="n">
+        <v>14</v>
+      </c>
+      <c r="M65" t="n">
+        <v>9</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.05212567858802541</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-0.1047373284892442</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.2124289890699309</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Austalian_Investment_Grade_Credit</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>108</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.3919287024588367</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.2183210470948332</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-0.04472272570609226</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.239326244993921</v>
+      </c>
+      <c r="K66" t="n">
+        <v>34.06940063091483</v>
+      </c>
+      <c r="L66" t="n">
+        <v>13</v>
+      </c>
+      <c r="M66" t="n">
+        <v>8.307692307692308</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.03330979345354609</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.004526999999999948</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.09000436011536328</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Austalian_Investment_Grade_Credit</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>52</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.4056102307308687</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1467925908658299</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-0.07586542404788288</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.6609566636423647</v>
+      </c>
+      <c r="K67" t="n">
+        <v>16.40378548895899</v>
+      </c>
+      <c r="L67" t="n">
+        <v>13</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.01644607804554587</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.001129185516220321</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.05500260671228419</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Austalian_Investment_Grade_Credit</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>59</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.3867764781009325</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1715993191971577</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-0.1035620842872564</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.7796267732602224</v>
+      </c>
+      <c r="K68" t="n">
+        <v>18.61198738170347</v>
+      </c>
+      <c r="L68" t="n">
+        <v>10</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.02326258638807779</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.0009255366018317002</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.07805273998853113</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Austalian_Investment_Grade_Credit</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>98</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.3144954663643668</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.3236032929537803</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-1.330840809090184</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.010778030303472</v>
+      </c>
+      <c r="K69" t="n">
+        <v>30.91482649842272</v>
+      </c>
+      <c r="L69" t="n">
+        <v>12</v>
+      </c>
+      <c r="M69" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.02625316982665905</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-0.004172402593761393</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.09293672205695325</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Australian_CPI_Linked_Bonds</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>108</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.3860803059708451</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.454381984621689</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-4.3118972460746</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5.58252622413555</v>
+      </c>
+      <c r="K70" t="n">
+        <v>34.06940063091483</v>
+      </c>
+      <c r="L70" t="n">
+        <v>13</v>
+      </c>
+      <c r="M70" t="n">
+        <v>8.307692307692308</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.03218175082462012</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-0.03517709057256846</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.08919996504449257</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Australian_CPI_Linked_Bonds</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>52</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.5238900516973722</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.533708518301683</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-2.22663051663729</v>
+      </c>
+      <c r="J71" t="n">
+        <v>4.70488677952541</v>
+      </c>
+      <c r="K71" t="n">
+        <v>16.40378548895899</v>
+      </c>
+      <c r="L71" t="n">
+        <v>13</v>
+      </c>
+      <c r="M71" t="n">
+        <v>4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.02078640332942703</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-0.004632119371121179</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.04261134379659848</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Australian_CPI_Linked_Bonds</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>59</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.4729340924634133</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.335555566603056</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-3.12470157576248</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3.4864510896722</v>
+      </c>
+      <c r="K72" t="n">
+        <v>18.61198738170347</v>
+      </c>
+      <c r="L72" t="n">
+        <v>10</v>
+      </c>
+      <c r="M72" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.028316278426221</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-0.03124701575762479</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.1094518981605275</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Aust</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Australian_CPI_Linked_Bonds</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>98</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.4247419166000658</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.910391592289321</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-5.4773212861424</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4.82468738774104</v>
+      </c>
+      <c r="K73" t="n">
+        <v>30.91482649842272</v>
+      </c>
+      <c r="L73" t="n">
+        <v>12</v>
+      </c>
+      <c r="M73" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.03553424791643464</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-0.08575577275028046</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.1460214332770982</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6577D0C3AE724BBB504F46D5A19401" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17afb16e0fbe716d3dcf2481b32b5550">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df76e320-99cb-4a11-b59f-8bf32867ab70" xmlns:ns3="c0789f30-979e-497b-8344-faefb3987540" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6d0bb8d4e6a5d6b988ea2ed2503dbb5" ns2:_="" ns3:_="">
+    <xsd:import namespace="df76e320-99cb-4a11-b59f-8bf32867ab70"/>
+    <xsd:import namespace="c0789f30-979e-497b-8344-faefb3987540"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="df76e320-99cb-4a11-b59f-8bf32867ab70" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2ea5f6a7-5373-4784-9cd5-4ca8be386d98" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0789f30-979e-497b-8344-faefb3987540" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f1100522-260f-4f17-9a31-47a12622b1e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c0789f30-979e-497b-8344-faefb3987540">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0789f30-979e-497b-8344-faefb3987540" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="df76e320-99cb-4a11-b59f-8bf32867ab70">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FE7FF8C-E41E-46F9-A5E2-77050B4711B5}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2A4D466-EB01-4CB7-A40D-45CB1824555B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6392D682-56AC-4F78-8A35-4EF70B70FAD3}"/>
 </file>
--- a/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66085423558476</v>
+        <v>1.674271465407753</v>
       </c>
       <c r="H2" t="n">
-        <v>3.844303865270501</v>
+        <v>3.838500542996565</v>
       </c>
       <c r="I2" t="n">
         <v>-10.29308361861639</v>
@@ -545,16 +545,16 @@
         <v>17.42999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>34.4954128440367</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="L2" t="n">
         <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>9.894736842105264</v>
+        <v>9.947368421052632</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1774969569522575</v>
+        <v>0.1800506296102232</v>
       </c>
       <c r="O2" t="n">
         <v>0.01526130786432289</v>
@@ -603,7 +603,7 @@
         <v>16.16500377295211</v>
       </c>
       <c r="K3" t="n">
-        <v>16.51376146788991</v>
+        <v>16.48351648351648</v>
       </c>
       <c r="L3" t="n">
         <v>18</v>
@@ -661,7 +661,7 @@
         <v>8.523157098428168</v>
       </c>
       <c r="K4" t="n">
-        <v>19.63302752293578</v>
+        <v>19.5970695970696</v>
       </c>
       <c r="L4" t="n">
         <v>18</v>
@@ -719,7 +719,7 @@
         <v>12.5359029000278</v>
       </c>
       <c r="K5" t="n">
-        <v>29.35779816513762</v>
+        <v>29.30402930402931</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>1.456502723589905</v>
+        <v>1.488630601920741</v>
       </c>
       <c r="H6" t="n">
-        <v>4.304656609520738</v>
+        <v>4.297483912302717</v>
       </c>
       <c r="I6" t="n">
         <v>-8.97730231120652</v>
@@ -777,16 +777,16 @@
         <v>16.1167748089563</v>
       </c>
       <c r="K6" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L6" t="n">
         <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1363545240636568</v>
+        <v>0.14132711197976</v>
       </c>
       <c r="O6" t="n">
         <v>-0.09264081476093833</v>
@@ -835,7 +835,7 @@
         <v>11.7821325405861</v>
       </c>
       <c r="K7" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -893,7 +893,7 @@
         <v>8.157897599276009</v>
       </c>
       <c r="K8" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
@@ -951,7 +951,7 @@
         <v>13.6888940729176</v>
       </c>
       <c r="K9" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L9" t="n">
         <v>12</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>1.545367764507353</v>
+        <v>1.656423997814999</v>
       </c>
       <c r="H10" t="n">
-        <v>4.026401837250746</v>
+        <v>4.020791323175327</v>
       </c>
       <c r="I10" t="n">
         <v>-4.724652064266159</v>
@@ -1009,16 +1009,16 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K10" t="n">
-        <v>42.5</v>
+        <v>43.20987654320987</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>11.33333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1831244553352133</v>
+        <v>0.2047502879737012</v>
       </c>
       <c r="O10" t="n">
         <v>0.06926769637694097</v>
@@ -1067,7 +1067,7 @@
         <v>7.09284827773554</v>
       </c>
       <c r="K11" t="n">
-        <v>8.75</v>
+        <v>8.641975308641975</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
@@ -1125,7 +1125,7 @@
         <v>7.65174934622371</v>
       </c>
       <c r="K12" t="n">
-        <v>6.25</v>
+        <v>6.172839506172839</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K13" t="n">
-        <v>42.5</v>
+        <v>41.9753086419753</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G14" t="n">
-        <v>1.391037311042302</v>
+        <v>1.397491411675935</v>
       </c>
       <c r="H14" t="n">
-        <v>4.223450032974992</v>
+        <v>4.204203025106291</v>
       </c>
       <c r="I14" t="n">
         <v>-7.39121056995352</v>
@@ -1241,16 +1241,16 @@
         <v>10.5507582207258</v>
       </c>
       <c r="K14" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L14" t="n">
         <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1322119707335318</v>
+        <v>0.1344083341164092</v>
       </c>
       <c r="O14" t="n">
         <v>-0.1107307878394987</v>
@@ -1299,7 +1299,7 @@
         <v>14.9951975592301</v>
       </c>
       <c r="K15" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L15" t="n">
         <v>12</v>
@@ -1357,7 +1357,7 @@
         <v>12.0388754904431</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
         <v>17.0568622218592</v>
       </c>
       <c r="K17" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L17" t="n">
         <v>12</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" t="n">
-        <v>1.014935391327171</v>
+        <v>1.016885580557459</v>
       </c>
       <c r="H18" t="n">
-        <v>3.528539640680341</v>
+        <v>3.512070909406839</v>
       </c>
       <c r="I18" t="n">
         <v>-9.00069743294255</v>
@@ -1473,16 +1473,16 @@
         <v>9.585535370371879</v>
       </c>
       <c r="K18" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L18" t="n">
         <v>12</v>
       </c>
       <c r="M18" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.09145747466591085</v>
+        <v>0.09254021825991228</v>
       </c>
       <c r="O18" t="n">
         <v>-0.06249589774862385</v>
@@ -1531,7 +1531,7 @@
         <v>10.6235569673087</v>
       </c>
       <c r="K19" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
@@ -1589,7 +1589,7 @@
         <v>11.9143823646577</v>
       </c>
       <c r="K20" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
         <v>6.793266873392841</v>
       </c>
       <c r="K21" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L21" t="n">
         <v>12</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8500926746393325</v>
+        <v>0.9226179268873453</v>
       </c>
       <c r="H22" t="n">
-        <v>5.255273811216077</v>
+        <v>5.284681836072688</v>
       </c>
       <c r="I22" t="n">
         <v>-10.7369500066555</v>
@@ -1705,19 +1705,19 @@
         <v>28.2407194114024</v>
       </c>
       <c r="K22" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L22" t="n">
         <v>12</v>
       </c>
       <c r="M22" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07820321347097516</v>
+        <v>0.08384583721945078</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2201671159179077</v>
+        <v>-0.1524556309362002</v>
       </c>
       <c r="P22" t="n">
         <v>0.3961971237699671</v>
@@ -1763,7 +1763,7 @@
         <v>10.1238105397411</v>
       </c>
       <c r="K23" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L23" t="n">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>13.2720975781699</v>
       </c>
       <c r="K24" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>25.211119079268</v>
       </c>
       <c r="K25" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L25" t="n">
         <v>12</v>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G26" t="n">
-        <v>1.902253453996314</v>
+        <v>1.931667955388996</v>
       </c>
       <c r="H26" t="n">
-        <v>4.086037239915052</v>
+        <v>4.078370843344476</v>
       </c>
       <c r="I26" t="n">
         <v>-9.635645143182661</v>
@@ -1937,22 +1937,22 @@
         <v>16.1158229524901</v>
       </c>
       <c r="K26" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L26" t="n">
         <v>12</v>
       </c>
       <c r="M26" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1837662420049963</v>
+        <v>0.1895890073794011</v>
       </c>
       <c r="O26" t="n">
         <v>-0.02947196847005373</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4255216721371256</v>
+        <v>0.4455950744466681</v>
       </c>
     </row>
     <row r="27">
@@ -1995,7 +1995,7 @@
         <v>9.768282119936639</v>
       </c>
       <c r="K27" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L27" t="n">
         <v>12</v>
@@ -2053,7 +2053,7 @@
         <v>8.49076575066875</v>
       </c>
       <c r="K28" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>12.07642730623</v>
       </c>
       <c r="K29" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L29" t="n">
         <v>12</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G30" t="n">
-        <v>1.109061151587155</v>
+        <v>1.111983071490986</v>
       </c>
       <c r="H30" t="n">
-        <v>3.954557161787932</v>
+        <v>3.936151673134672</v>
       </c>
       <c r="I30" t="n">
         <v>-10.8112251477361</v>
@@ -2169,16 +2169,16 @@
         <v>9.39119756344274</v>
       </c>
       <c r="K30" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L30" t="n">
         <v>12</v>
       </c>
       <c r="M30" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1072992395182234</v>
+        <v>0.1084599444492949</v>
       </c>
       <c r="O30" t="n">
         <v>-0.2594245775460494</v>
@@ -2227,7 +2227,7 @@
         <v>10.5168773145652</v>
       </c>
       <c r="K31" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L31" t="n">
         <v>12</v>
@@ -2285,7 +2285,7 @@
         <v>12.0090481450406</v>
       </c>
       <c r="K32" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>20.1357853233765</v>
       </c>
       <c r="K33" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L33" t="n">
         <v>12</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G34" t="n">
-        <v>1.316453063907418</v>
+        <v>1.345163862317833</v>
       </c>
       <c r="H34" t="n">
-        <v>3.882940192696579</v>
+        <v>3.87625352287444</v>
       </c>
       <c r="I34" t="n">
         <v>-11.3876720879084</v>
@@ -2401,16 +2401,16 @@
         <v>12.109209792019</v>
       </c>
       <c r="K34" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L34" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1239991756367903</v>
+        <v>0.1286614192692487</v>
       </c>
       <c r="O34" t="n">
         <v>-0.08087269380805873</v>
@@ -2459,7 +2459,7 @@
         <v>8.0175198917632</v>
       </c>
       <c r="K35" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L35" t="n">
         <v>12</v>
@@ -2517,7 +2517,7 @@
         <v>8.33833543505675</v>
       </c>
       <c r="K36" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L36" t="n">
         <v>10</v>
@@ -2575,7 +2575,7 @@
         <v>15.3362226075419</v>
       </c>
       <c r="K37" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L37" t="n">
         <v>12</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G38" t="n">
-        <v>1.583862459137402</v>
+        <v>1.743573299611279</v>
       </c>
       <c r="H38" t="n">
-        <v>6.147623011817134</v>
+        <v>6.339942921965543</v>
       </c>
       <c r="I38" t="n">
         <v>-12.2948760443384</v>
@@ -2633,22 +2633,22 @@
         <v>19.7034328806292</v>
       </c>
       <c r="K38" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L38" t="n">
         <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1519597065963022</v>
+        <v>0.175826118767501</v>
       </c>
       <c r="O38" t="n">
         <v>-0.2342435165396028</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5207482806671548</v>
+        <v>0.8071452267215398</v>
       </c>
     </row>
     <row r="39">
@@ -2691,7 +2691,7 @@
         <v>15.3631100623459</v>
       </c>
       <c r="K39" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -2749,7 +2749,7 @@
         <v>21.9468390804598</v>
       </c>
       <c r="K40" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L40" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>29.6127554257064</v>
       </c>
       <c r="K41" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L41" t="n">
         <v>12</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G42" t="n">
-        <v>1.626866338579104</v>
+        <v>1.630534670498116</v>
       </c>
       <c r="H42" t="n">
-        <v>4.96098088233609</v>
+        <v>4.937891472267101</v>
       </c>
       <c r="I42" t="n">
         <v>-10.9393768664177</v>
@@ -2865,16 +2865,16 @@
         <v>14.5795620340833</v>
       </c>
       <c r="K42" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L42" t="n">
         <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1529391006137088</v>
+        <v>0.1545216577041648</v>
       </c>
       <c r="O42" t="n">
         <v>-0.06815823317850678</v>
@@ -2923,7 +2923,7 @@
         <v>10.463139776602</v>
       </c>
       <c r="K43" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L43" t="n">
         <v>12</v>
@@ -2981,7 +2981,7 @@
         <v>11.502191267126</v>
       </c>
       <c r="K44" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L44" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K45" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L45" t="n">
         <v>12</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G46" t="n">
-        <v>1.500067138249088</v>
+        <v>1.58615563110962</v>
       </c>
       <c r="H46" t="n">
-        <v>4.689188130623344</v>
+        <v>4.662899694824272</v>
       </c>
       <c r="I46" t="n">
         <v>-7.641550815508549</v>
@@ -3097,16 +3097,16 @@
         <v>13.2283841318109</v>
       </c>
       <c r="K46" t="n">
-        <v>38.83495145631068</v>
+        <v>39.42307692307692</v>
       </c>
       <c r="L46" t="n">
         <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1536330293644707</v>
+        <v>0.1685524205733006</v>
       </c>
       <c r="O46" t="n">
         <v>0.01998150231082008</v>
@@ -3155,7 +3155,7 @@
         <v>11.9534070082495</v>
       </c>
       <c r="K47" t="n">
-        <v>12.62135922330097</v>
+        <v>12.5</v>
       </c>
       <c r="L47" t="n">
         <v>6</v>
@@ -3213,7 +3213,7 @@
         <v>5.99996918574318</v>
       </c>
       <c r="K48" t="n">
-        <v>4.854368932038835</v>
+        <v>4.807692307692308</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3271,7 +3271,7 @@
         <v>14.1184473609332</v>
       </c>
       <c r="K49" t="n">
-        <v>43.68932038834951</v>
+        <v>43.26923076923077</v>
       </c>
       <c r="L49" t="n">
         <v>5</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8691050171989759</v>
+        <v>0.9113571552830129</v>
       </c>
       <c r="H50" t="n">
-        <v>4.071497655130523</v>
+        <v>4.076146871019589</v>
       </c>
       <c r="I50" t="n">
         <v>-9.48046022451167</v>
@@ -3329,16 +3329,16 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K50" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L50" t="n">
         <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>0.08054328644176401</v>
+        <v>0.08594974460138598</v>
       </c>
       <c r="O50" t="n">
         <v>-0.1552012693445518</v>
@@ -3387,7 +3387,7 @@
         <v>13.0214086312522</v>
       </c>
       <c r="K51" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L51" t="n">
         <v>12</v>
@@ -3445,7 +3445,7 @@
         <v>12.2238347773583</v>
       </c>
       <c r="K52" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L52" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K53" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L53" t="n">
         <v>12</v>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7368961166608688</v>
+        <v>0.7329523007129376</v>
       </c>
       <c r="H54" t="n">
-        <v>3.626588581944838</v>
+        <v>3.609834802314882</v>
       </c>
       <c r="I54" t="n">
         <v>-8.016951710911901</v>
@@ -3561,16 +3561,16 @@
         <v>9.074501372422739</v>
       </c>
       <c r="K54" t="n">
-        <v>35.43046357615894</v>
+        <v>35.64356435643564</v>
       </c>
       <c r="L54" t="n">
         <v>12</v>
       </c>
       <c r="M54" t="n">
-        <v>8.916666666666666</v>
+        <v>9</v>
       </c>
       <c r="N54" t="n">
-        <v>0.07203938989856955</v>
+        <v>0.07236237801351902</v>
       </c>
       <c r="O54" t="n">
         <v>-0.184079252512853</v>
@@ -3619,7 +3619,7 @@
         <v>8.09206131391011</v>
       </c>
       <c r="K55" t="n">
-        <v>14.23841059602649</v>
+        <v>14.19141914191419</v>
       </c>
       <c r="L55" t="n">
         <v>12</v>
@@ -3677,7 +3677,7 @@
         <v>6.97269921720136</v>
       </c>
       <c r="K56" t="n">
-        <v>19.5364238410596</v>
+        <v>19.47194719471947</v>
       </c>
       <c r="L56" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
         <v>20.8483922702477</v>
       </c>
       <c r="K57" t="n">
-        <v>30.79470198675497</v>
+        <v>30.69306930693069</v>
       </c>
       <c r="L57" t="n">
         <v>12</v>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5764270921737074</v>
+        <v>0.5739802149229897</v>
       </c>
       <c r="H58" t="n">
-        <v>1.181667925920913</v>
+        <v>1.1785751495616</v>
       </c>
       <c r="I58" t="n">
         <v>-3.5808884985017</v>
@@ -3793,16 +3793,16 @@
         <v>3.503733642227802</v>
       </c>
       <c r="K58" t="n">
-        <v>39.34426229508197</v>
+        <v>39.48598130841122</v>
       </c>
       <c r="L58" t="n">
         <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>11.2</v>
+        <v>11.26666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>0.07166159676513875</v>
+        <v>0.07177670418226999</v>
       </c>
       <c r="O58" t="n">
         <v>-0.0120745479938501</v>
@@ -3851,7 +3851,7 @@
         <v>3.402309746334153</v>
       </c>
       <c r="K59" t="n">
-        <v>13.81733021077283</v>
+        <v>13.78504672897196</v>
       </c>
       <c r="L59" t="n">
         <v>14</v>
@@ -3909,7 +3909,7 @@
         <v>4.116485870291786</v>
       </c>
       <c r="K60" t="n">
-        <v>17.33021077283372</v>
+        <v>17.28971962616822</v>
       </c>
       <c r="L60" t="n">
         <v>14</v>
@@ -3967,7 +3967,7 @@
         <v>4.260323410130962</v>
       </c>
       <c r="K61" t="n">
-        <v>29.50819672131147</v>
+        <v>29.4392523364486</v>
       </c>
       <c r="L61" t="n">
         <v>14</v>
@@ -4010,13 +4010,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5318193736509128</v>
+        <v>0.5289252157931822</v>
       </c>
       <c r="H62" t="n">
-        <v>1.314382132344291</v>
+        <v>1.311208243193264</v>
       </c>
       <c r="I62" t="n">
         <v>-4.206622271745363</v>
@@ -4025,16 +4025,16 @@
         <v>3.744396140912065</v>
       </c>
       <c r="K62" t="n">
-        <v>39.46188340807175</v>
+        <v>39.59731543624161</v>
       </c>
       <c r="L62" t="n">
         <v>16</v>
       </c>
       <c r="M62" t="n">
-        <v>11</v>
+        <v>11.0625</v>
       </c>
       <c r="N62" t="n">
-        <v>0.06450120300299837</v>
+        <v>0.06451405703929622</v>
       </c>
       <c r="O62" t="n">
         <v>-0.02204332401546116</v>
@@ -4083,7 +4083,7 @@
         <v>3.553979827111342</v>
       </c>
       <c r="K63" t="n">
-        <v>13.22869955156951</v>
+        <v>13.19910514541387</v>
       </c>
       <c r="L63" t="n">
         <v>14</v>
@@ -4141,7 +4141,7 @@
         <v>4.289426931116491</v>
       </c>
       <c r="K64" t="n">
-        <v>19.05829596412556</v>
+        <v>19.01565995525727</v>
       </c>
       <c r="L64" t="n">
         <v>14</v>
@@ -4199,7 +4199,7 @@
         <v>4.441637267010878</v>
       </c>
       <c r="K65" t="n">
-        <v>28.25112107623318</v>
+        <v>28.18791946308725</v>
       </c>
       <c r="L65" t="n">
         <v>14</v>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3919287024588367</v>
+        <v>0.3942406345568538</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2183210470948332</v>
+        <v>0.2186443546195243</v>
       </c>
       <c r="I66" t="n">
         <v>-0.04472272570609226</v>
@@ -4257,16 +4257,16 @@
         <v>1.239326244993921</v>
       </c>
       <c r="K66" t="n">
-        <v>34.06940063091483</v>
+        <v>34.27672955974842</v>
       </c>
       <c r="L66" t="n">
         <v>13</v>
       </c>
       <c r="M66" t="n">
-        <v>8.307692307692308</v>
+        <v>8.384615384615385</v>
       </c>
       <c r="N66" t="n">
-        <v>0.03330979345354609</v>
+        <v>0.03384221932886008</v>
       </c>
       <c r="O66" t="n">
         <v>0.004526999999999948</v>
@@ -4315,7 +4315,7 @@
         <v>0.6609566636423647</v>
       </c>
       <c r="K67" t="n">
-        <v>16.40378548895899</v>
+        <v>16.35220125786163</v>
       </c>
       <c r="L67" t="n">
         <v>13</v>
@@ -4373,7 +4373,7 @@
         <v>0.7796267732602224</v>
       </c>
       <c r="K68" t="n">
-        <v>18.61198738170347</v>
+        <v>18.55345911949685</v>
       </c>
       <c r="L68" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
         <v>1.010778030303472</v>
       </c>
       <c r="K69" t="n">
-        <v>30.91482649842272</v>
+        <v>30.81761006289308</v>
       </c>
       <c r="L69" t="n">
         <v>12</v>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3860803059708451</v>
+        <v>0.3863125440733977</v>
       </c>
       <c r="H70" t="n">
-        <v>1.454381984621689</v>
+        <v>1.447635106395172</v>
       </c>
       <c r="I70" t="n">
         <v>-4.3118972460746</v>
@@ -4489,16 +4489,16 @@
         <v>5.58252622413555</v>
       </c>
       <c r="K70" t="n">
-        <v>34.06940063091483</v>
+        <v>34.27672955974842</v>
       </c>
       <c r="L70" t="n">
         <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>8.307692307692308</v>
+        <v>8.384615384615385</v>
       </c>
       <c r="N70" t="n">
-        <v>0.03218175082462012</v>
+        <v>0.03250451525653873</v>
       </c>
       <c r="O70" t="n">
         <v>-0.03517709057256846</v>
@@ -4547,7 +4547,7 @@
         <v>4.70488677952541</v>
       </c>
       <c r="K71" t="n">
-        <v>16.40378548895899</v>
+        <v>16.35220125786163</v>
       </c>
       <c r="L71" t="n">
         <v>13</v>
@@ -4605,7 +4605,7 @@
         <v>3.4864510896722</v>
       </c>
       <c r="K72" t="n">
-        <v>18.61198738170347</v>
+        <v>18.55345911949685</v>
       </c>
       <c r="L72" t="n">
         <v>10</v>
@@ -4663,7 +4663,7 @@
         <v>4.82468738774104</v>
       </c>
       <c r="K73" t="n">
-        <v>30.91482649842272</v>
+        <v>30.81761006289308</v>
       </c>
       <c r="L73" t="n">
         <v>12</v>
@@ -4962,13 +4962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FE7FF8C-E41E-46F9-A5E2-77050B4711B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0E38D6-1DE7-41D0-AD24-5DE04B2F9173}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2A4D466-EB01-4CB7-A40D-45CB1824555B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092EC725-5A16-43BC-90B7-65F9CB423854}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6392D682-56AC-4F78-8A35-4EF70B70FAD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC3904F-6A92-47A9-8A1E-832BC7E71D72}"/>
 </file>
--- a/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regSummary_Aust.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G2" t="n">
-        <v>1.674271465407753</v>
+        <v>1.713684578012793</v>
       </c>
       <c r="H2" t="n">
-        <v>3.838500542996565</v>
+        <v>3.82113034851632</v>
       </c>
       <c r="I2" t="n">
         <v>-10.29308361861639</v>
@@ -545,16 +545,16 @@
         <v>17.42999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>34.61538461538461</v>
+        <v>34.97267759562842</v>
       </c>
       <c r="L2" t="n">
         <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>9.947368421052632</v>
+        <v>10.10526315789474</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1800506296102232</v>
+        <v>0.1883728483560306</v>
       </c>
       <c r="O2" t="n">
         <v>0.01526130786432289</v>
@@ -603,7 +603,7 @@
         <v>16.16500377295211</v>
       </c>
       <c r="K3" t="n">
-        <v>16.48351648351648</v>
+        <v>16.39344262295082</v>
       </c>
       <c r="L3" t="n">
         <v>18</v>
@@ -661,7 +661,7 @@
         <v>8.523157098428168</v>
       </c>
       <c r="K4" t="n">
-        <v>19.5970695970696</v>
+        <v>19.48998178506375</v>
       </c>
       <c r="L4" t="n">
         <v>18</v>
@@ -719,7 +719,7 @@
         <v>12.5359029000278</v>
       </c>
       <c r="K5" t="n">
-        <v>29.30402930402931</v>
+        <v>29.14389799635702</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G6" t="n">
-        <v>1.488630601920741</v>
+        <v>1.581540952769375</v>
       </c>
       <c r="H6" t="n">
-        <v>4.297483912302717</v>
+        <v>4.275309853025708</v>
       </c>
       <c r="I6" t="n">
         <v>-8.97730231120652</v>
@@ -777,22 +777,22 @@
         <v>16.1167748089563</v>
       </c>
       <c r="K6" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L6" t="n">
         <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.14132711197976</v>
+        <v>0.1577635328976318</v>
       </c>
       <c r="O6" t="n">
         <v>-0.09264081476093833</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3307534453748742</v>
+        <v>0.4681800639130318</v>
       </c>
     </row>
     <row r="7">
@@ -835,7 +835,7 @@
         <v>11.7821325405861</v>
       </c>
       <c r="K7" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L7" t="n">
         <v>12</v>
@@ -893,7 +893,7 @@
         <v>8.157897599276009</v>
       </c>
       <c r="K8" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
@@ -951,7 +951,7 @@
         <v>13.6888940729176</v>
       </c>
       <c r="K9" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L9" t="n">
         <v>12</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>1.656423997814999</v>
+        <v>1.954522308272365</v>
       </c>
       <c r="H10" t="n">
-        <v>4.020791323175327</v>
+        <v>3.990074480292189</v>
       </c>
       <c r="I10" t="n">
         <v>-4.724652064266159</v>
@@ -1009,22 +1009,22 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K10" t="n">
-        <v>43.20987654320987</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>11.66666666666667</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2047502879737012</v>
+        <v>0.2769352536758974</v>
       </c>
       <c r="O10" t="n">
         <v>0.06926769637694097</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2858220548416497</v>
+        <v>0.4757160098091016</v>
       </c>
     </row>
     <row r="11">
@@ -1067,7 +1067,7 @@
         <v>7.09284827773554</v>
       </c>
       <c r="K11" t="n">
-        <v>8.641975308641975</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
@@ -1125,7 +1125,7 @@
         <v>7.65174934622371</v>
       </c>
       <c r="K12" t="n">
-        <v>6.172839506172839</v>
+        <v>5.952380952380952</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K13" t="n">
-        <v>41.9753086419753</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G14" t="n">
-        <v>1.397491411675935</v>
+        <v>1.416155972967794</v>
       </c>
       <c r="H14" t="n">
-        <v>4.204203025106291</v>
+        <v>4.148002409807923</v>
       </c>
       <c r="I14" t="n">
         <v>-7.39121056995352</v>
@@ -1241,16 +1241,16 @@
         <v>10.5507582207258</v>
       </c>
       <c r="K14" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L14" t="n">
         <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1344083341164092</v>
+        <v>0.1412764457589632</v>
       </c>
       <c r="O14" t="n">
         <v>-0.1107307878394987</v>
@@ -1299,7 +1299,7 @@
         <v>14.9951975592301</v>
       </c>
       <c r="K15" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L15" t="n">
         <v>12</v>
@@ -1357,7 +1357,7 @@
         <v>12.0388754904431</v>
       </c>
       <c r="K16" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
         <v>17.0568622218592</v>
       </c>
       <c r="K17" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L17" t="n">
         <v>12</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
-        <v>1.016885580557459</v>
+        <v>1.022525316980187</v>
       </c>
       <c r="H18" t="n">
-        <v>3.512070909406839</v>
+        <v>3.464014750467564</v>
       </c>
       <c r="I18" t="n">
         <v>-9.00069743294255</v>
@@ -1473,16 +1473,16 @@
         <v>9.585535370371879</v>
       </c>
       <c r="K18" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L18" t="n">
         <v>12</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0.09254021825991228</v>
+        <v>0.09586871930508097</v>
       </c>
       <c r="O18" t="n">
         <v>-0.06249589774862385</v>
@@ -1531,7 +1531,7 @@
         <v>10.6235569673087</v>
       </c>
       <c r="K19" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
@@ -1589,7 +1589,7 @@
         <v>11.9143823646577</v>
       </c>
       <c r="K20" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
         <v>6.793266873392841</v>
       </c>
       <c r="K21" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L21" t="n">
         <v>12</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9226179268873453</v>
+        <v>1.132353115820788</v>
       </c>
       <c r="H22" t="n">
-        <v>5.284681836072688</v>
+        <v>5.363225528898509</v>
       </c>
       <c r="I22" t="n">
         <v>-10.7369500066555</v>
@@ -1705,19 +1705,19 @@
         <v>28.2407194114024</v>
       </c>
       <c r="K22" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L22" t="n">
         <v>12</v>
       </c>
       <c r="M22" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0.08384583721945078</v>
+        <v>0.1038871973680621</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1524556309362002</v>
+        <v>-0.1052556714819162</v>
       </c>
       <c r="P22" t="n">
         <v>0.3961971237699671</v>
@@ -1763,7 +1763,7 @@
         <v>10.1238105397411</v>
       </c>
       <c r="K23" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L23" t="n">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>13.2720975781699</v>
       </c>
       <c r="K24" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>25.211119079268</v>
       </c>
       <c r="K25" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L25" t="n">
         <v>12</v>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G26" t="n">
-        <v>1.931667955388996</v>
+        <v>2.016731513470534</v>
       </c>
       <c r="H26" t="n">
-        <v>4.078370843344476</v>
+        <v>4.054915005446466</v>
       </c>
       <c r="I26" t="n">
         <v>-9.635645143182661</v>
@@ -1937,22 +1937,22 @@
         <v>16.1158229524901</v>
       </c>
       <c r="K26" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L26" t="n">
         <v>12</v>
       </c>
       <c r="M26" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1895890073794011</v>
+        <v>0.2088925854216593</v>
       </c>
       <c r="O26" t="n">
         <v>-0.02947196847005373</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4455950744466681</v>
+        <v>0.6772380109537666</v>
       </c>
     </row>
     <row r="27">
@@ -1995,7 +1995,7 @@
         <v>9.768282119936639</v>
       </c>
       <c r="K27" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L27" t="n">
         <v>12</v>
@@ -2053,7 +2053,7 @@
         <v>8.49076575066875</v>
       </c>
       <c r="K28" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>12.07642730623</v>
       </c>
       <c r="K29" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L29" t="n">
         <v>12</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G30" t="n">
-        <v>1.111983071490986</v>
+        <v>1.120432947969633</v>
       </c>
       <c r="H30" t="n">
-        <v>3.936151673134672</v>
+        <v>3.882439890534982</v>
       </c>
       <c r="I30" t="n">
         <v>-10.8112251477361</v>
@@ -2169,16 +2169,16 @@
         <v>9.39119756344274</v>
       </c>
       <c r="K30" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L30" t="n">
         <v>12</v>
       </c>
       <c r="M30" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1084599444492949</v>
+        <v>0.1120422192891994</v>
       </c>
       <c r="O30" t="n">
         <v>-0.2594245775460494</v>
@@ -2227,7 +2227,7 @@
         <v>10.5168773145652</v>
       </c>
       <c r="K31" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L31" t="n">
         <v>12</v>
@@ -2285,7 +2285,7 @@
         <v>12.0090481450406</v>
       </c>
       <c r="K32" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>20.1357853233765</v>
       </c>
       <c r="K33" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L33" t="n">
         <v>12</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G34" t="n">
-        <v>1.345163862317833</v>
+        <v>1.428192387450653</v>
       </c>
       <c r="H34" t="n">
-        <v>3.87625352287444</v>
+        <v>3.855643910347306</v>
       </c>
       <c r="I34" t="n">
         <v>-11.3876720879084</v>
@@ -2401,22 +2401,22 @@
         <v>12.109209792019</v>
       </c>
       <c r="K34" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L34" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1286614192692487</v>
+        <v>0.1439205887023776</v>
       </c>
       <c r="O34" t="n">
         <v>-0.08087269380805873</v>
       </c>
       <c r="P34" t="n">
-        <v>0.3979110146234845</v>
+        <v>0.5056212790040804</v>
       </c>
     </row>
     <row r="35">
@@ -2459,7 +2459,7 @@
         <v>8.0175198917632</v>
       </c>
       <c r="K35" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L35" t="n">
         <v>12</v>
@@ -2517,7 +2517,7 @@
         <v>8.33833543505675</v>
       </c>
       <c r="K36" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L36" t="n">
         <v>10</v>
@@ -2575,7 +2575,7 @@
         <v>15.3362226075419</v>
       </c>
       <c r="K37" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L37" t="n">
         <v>12</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G38" t="n">
-        <v>1.743573299611279</v>
+        <v>2.205439784224926</v>
       </c>
       <c r="H38" t="n">
-        <v>6.339942921965543</v>
+        <v>6.844560597486816</v>
       </c>
       <c r="I38" t="n">
         <v>-12.2948760443384</v>
@@ -2633,22 +2633,22 @@
         <v>19.7034328806292</v>
       </c>
       <c r="K38" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L38" t="n">
         <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N38" t="n">
-        <v>0.175826118767501</v>
+        <v>0.2779386720092691</v>
       </c>
       <c r="O38" t="n">
         <v>-0.2342435165396028</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8071452267215398</v>
+        <v>2.032495865622757</v>
       </c>
     </row>
     <row r="39">
@@ -2691,7 +2691,7 @@
         <v>15.3631100623459</v>
       </c>
       <c r="K39" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -2749,7 +2749,7 @@
         <v>21.9468390804598</v>
       </c>
       <c r="K40" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L40" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>29.6127554257064</v>
       </c>
       <c r="K41" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L41" t="n">
         <v>12</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G42" t="n">
-        <v>1.630534670498116</v>
+        <v>1.641143089831474</v>
       </c>
       <c r="H42" t="n">
-        <v>4.937891472267101</v>
+        <v>4.870510826877868</v>
       </c>
       <c r="I42" t="n">
         <v>-10.9393768664177</v>
@@ -2865,16 +2865,16 @@
         <v>14.5795620340833</v>
       </c>
       <c r="K42" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L42" t="n">
         <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1545216577041648</v>
+        <v>0.1594640280264652</v>
       </c>
       <c r="O42" t="n">
         <v>-0.06815823317850678</v>
@@ -2923,7 +2923,7 @@
         <v>10.463139776602</v>
       </c>
       <c r="K43" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L43" t="n">
         <v>12</v>
@@ -2981,7 +2981,7 @@
         <v>11.502191267126</v>
       </c>
       <c r="K44" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L44" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K45" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L45" t="n">
         <v>12</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58615563110962</v>
+        <v>1.820942429820162</v>
       </c>
       <c r="H46" t="n">
-        <v>4.662899694824272</v>
+        <v>4.582204574668197</v>
       </c>
       <c r="I46" t="n">
         <v>-7.641550815508549</v>
@@ -3097,22 +3097,22 @@
         <v>13.2283841318109</v>
       </c>
       <c r="K46" t="n">
-        <v>39.42307692307692</v>
+        <v>41.1214953271028</v>
       </c>
       <c r="L46" t="n">
         <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1685524205733006</v>
+        <v>0.2179658634208771</v>
       </c>
       <c r="O46" t="n">
         <v>0.01998150231082008</v>
       </c>
       <c r="P46" t="n">
-        <v>0.3138540007036315</v>
+        <v>0.4438359003309973</v>
       </c>
     </row>
     <row r="47">
@@ -3155,7 +3155,7 @@
         <v>11.9534070082495</v>
       </c>
       <c r="K47" t="n">
-        <v>12.5</v>
+        <v>12.14953271028037</v>
       </c>
       <c r="L47" t="n">
         <v>6</v>
@@ -3213,7 +3213,7 @@
         <v>5.99996918574318</v>
       </c>
       <c r="K48" t="n">
-        <v>4.807692307692308</v>
+        <v>4.672897196261682</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3271,7 +3271,7 @@
         <v>14.1184473609332</v>
       </c>
       <c r="K49" t="n">
-        <v>43.26923076923077</v>
+        <v>42.05607476635514</v>
       </c>
       <c r="L49" t="n">
         <v>5</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9113571552830129</v>
+        <v>1.033545770823336</v>
       </c>
       <c r="H50" t="n">
-        <v>4.076146871019589</v>
+        <v>4.087077924219556</v>
       </c>
       <c r="I50" t="n">
         <v>-9.48046022451167</v>
@@ -3329,22 +3329,22 @@
         <v>14.3514762853692</v>
       </c>
       <c r="K50" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L50" t="n">
         <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0.08594974460138598</v>
+        <v>0.103995986026935</v>
       </c>
       <c r="O50" t="n">
         <v>-0.1552012693445518</v>
       </c>
       <c r="P50" t="n">
-        <v>0.296657165512999</v>
+        <v>0.4757160098091016</v>
       </c>
     </row>
     <row r="51">
@@ -3387,7 +3387,7 @@
         <v>13.0214086312522</v>
       </c>
       <c r="K51" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L51" t="n">
         <v>12</v>
@@ -3445,7 +3445,7 @@
         <v>12.2238347773583</v>
       </c>
       <c r="K52" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L52" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>8.523880774371349</v>
       </c>
       <c r="K53" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L53" t="n">
         <v>12</v>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7329523007129376</v>
+        <v>0.7215472113500014</v>
       </c>
       <c r="H54" t="n">
-        <v>3.609834802314882</v>
+        <v>3.560933055776828</v>
       </c>
       <c r="I54" t="n">
         <v>-8.016951710911901</v>
@@ -3561,16 +3561,16 @@
         <v>9.074501372422739</v>
       </c>
       <c r="K54" t="n">
-        <v>35.64356435643564</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="L54" t="n">
         <v>12</v>
       </c>
       <c r="M54" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0.07236237801351902</v>
+        <v>0.07333738112153966</v>
       </c>
       <c r="O54" t="n">
         <v>-0.184079252512853</v>
@@ -3619,7 +3619,7 @@
         <v>8.09206131391011</v>
       </c>
       <c r="K55" t="n">
-        <v>14.19141914191419</v>
+        <v>14.05228758169935</v>
       </c>
       <c r="L55" t="n">
         <v>12</v>
@@ -3677,7 +3677,7 @@
         <v>6.97269921720136</v>
       </c>
       <c r="K56" t="n">
-        <v>19.47194719471947</v>
+        <v>19.28104575163399</v>
       </c>
       <c r="L56" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
         <v>20.8483922702477</v>
       </c>
       <c r="K57" t="n">
-        <v>30.69306930693069</v>
+        <v>30.3921568627451</v>
       </c>
       <c r="L57" t="n">
         <v>12</v>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5739802149229897</v>
+        <v>0.5668102955371656</v>
       </c>
       <c r="H58" t="n">
-        <v>1.1785751495616</v>
+        <v>1.169437119409183</v>
       </c>
       <c r="I58" t="n">
         <v>-3.5808884985017</v>
@@ -3793,16 +3793,16 @@
         <v>3.503733642227802</v>
       </c>
       <c r="K58" t="n">
-        <v>39.48598130841122</v>
+        <v>39.90719257540603</v>
       </c>
       <c r="L58" t="n">
         <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>11.26666666666667</v>
+        <v>11.46666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>0.07177670418226999</v>
+        <v>0.07212315274934913</v>
       </c>
       <c r="O58" t="n">
         <v>-0.0120745479938501</v>
@@ -3851,7 +3851,7 @@
         <v>3.402309746334153</v>
       </c>
       <c r="K59" t="n">
-        <v>13.78504672897196</v>
+        <v>13.68909512761021</v>
       </c>
       <c r="L59" t="n">
         <v>14</v>
@@ -3909,7 +3909,7 @@
         <v>4.116485870291786</v>
       </c>
       <c r="K60" t="n">
-        <v>17.28971962616822</v>
+        <v>17.16937354988399</v>
       </c>
       <c r="L60" t="n">
         <v>14</v>
@@ -3967,7 +3967,7 @@
         <v>4.260323410130962</v>
       </c>
       <c r="K61" t="n">
-        <v>29.4392523364486</v>
+        <v>29.23433874709977</v>
       </c>
       <c r="L61" t="n">
         <v>14</v>
@@ -4010,13 +4010,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5289252157931822</v>
+        <v>0.5204356860771723</v>
       </c>
       <c r="H62" t="n">
-        <v>1.311208243193264</v>
+        <v>1.301817397226853</v>
       </c>
       <c r="I62" t="n">
         <v>-4.206622271745363</v>
@@ -4025,16 +4025,16 @@
         <v>3.744396140912065</v>
       </c>
       <c r="K62" t="n">
-        <v>39.59731543624161</v>
+        <v>40</v>
       </c>
       <c r="L62" t="n">
         <v>16</v>
       </c>
       <c r="M62" t="n">
-        <v>11.0625</v>
+        <v>11.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0.06451405703929622</v>
+        <v>0.06455263423058782</v>
       </c>
       <c r="O62" t="n">
         <v>-0.02204332401546116</v>
@@ -4083,7 +4083,7 @@
         <v>3.553979827111342</v>
       </c>
       <c r="K63" t="n">
-        <v>13.19910514541387</v>
+        <v>13.11111111111111</v>
       </c>
       <c r="L63" t="n">
         <v>14</v>
@@ -4141,7 +4141,7 @@
         <v>4.289426931116491</v>
       </c>
       <c r="K64" t="n">
-        <v>19.01565995525727</v>
+        <v>18.88888888888889</v>
       </c>
       <c r="L64" t="n">
         <v>14</v>
@@ -4199,7 +4199,7 @@
         <v>4.441637267010878</v>
       </c>
       <c r="K65" t="n">
-        <v>28.18791946308725</v>
+        <v>28</v>
       </c>
       <c r="L65" t="n">
         <v>14</v>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3942406345568538</v>
+        <v>0.4009287238404034</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2186443546195243</v>
+        <v>0.2194383018119267</v>
       </c>
       <c r="I66" t="n">
         <v>-0.04472272570609226</v>
@@ -4257,22 +4257,22 @@
         <v>1.239326244993921</v>
       </c>
       <c r="K66" t="n">
-        <v>34.27672955974842</v>
+        <v>34.89096573208722</v>
       </c>
       <c r="L66" t="n">
         <v>13</v>
       </c>
       <c r="M66" t="n">
-        <v>8.384615384615385</v>
+        <v>8.615384615384615</v>
       </c>
       <c r="N66" t="n">
-        <v>0.03384221932886008</v>
+        <v>0.03546015608134798</v>
       </c>
       <c r="O66" t="n">
         <v>0.004526999999999948</v>
       </c>
       <c r="P66" t="n">
-        <v>0.09000436011536328</v>
+        <v>0.102845446233881</v>
       </c>
     </row>
     <row r="67">
@@ -4315,7 +4315,7 @@
         <v>0.6609566636423647</v>
       </c>
       <c r="K67" t="n">
-        <v>16.35220125786163</v>
+        <v>16.1993769470405</v>
       </c>
       <c r="L67" t="n">
         <v>13</v>
@@ -4373,7 +4373,7 @@
         <v>0.7796267732602224</v>
       </c>
       <c r="K68" t="n">
-        <v>18.55345911949685</v>
+        <v>18.38006230529595</v>
       </c>
       <c r="L68" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
         <v>1.010778030303472</v>
       </c>
       <c r="K69" t="n">
-        <v>30.81761006289308</v>
+        <v>30.52959501557632</v>
       </c>
       <c r="L69" t="n">
         <v>12</v>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3863125440733977</v>
+        <v>0.3869843757272108</v>
       </c>
       <c r="H70" t="n">
-        <v>1.447635106395172</v>
+        <v>1.427944266905631</v>
       </c>
       <c r="I70" t="n">
         <v>-4.3118972460746</v>
@@ -4489,16 +4489,16 @@
         <v>5.58252622413555</v>
       </c>
       <c r="K70" t="n">
-        <v>34.27672955974842</v>
+        <v>34.89096573208722</v>
       </c>
       <c r="L70" t="n">
         <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>8.384615384615385</v>
+        <v>8.615384615384615</v>
       </c>
       <c r="N70" t="n">
-        <v>0.03250451525653873</v>
+        <v>0.03348079743136546</v>
       </c>
       <c r="O70" t="n">
         <v>-0.03517709057256846</v>
@@ -4547,7 +4547,7 @@
         <v>4.70488677952541</v>
       </c>
       <c r="K71" t="n">
-        <v>16.35220125786163</v>
+        <v>16.1993769470405</v>
       </c>
       <c r="L71" t="n">
         <v>13</v>
@@ -4605,7 +4605,7 @@
         <v>3.4864510896722</v>
       </c>
       <c r="K72" t="n">
-        <v>18.55345911949685</v>
+        <v>18.38006230529595</v>
       </c>
       <c r="L72" t="n">
         <v>10</v>
@@ -4663,7 +4663,7 @@
         <v>4.82468738774104</v>
       </c>
       <c r="K73" t="n">
-        <v>30.81761006289308</v>
+        <v>30.52959501557632</v>
       </c>
       <c r="L73" t="n">
         <v>12</v>
@@ -4962,13 +4962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0E38D6-1DE7-41D0-AD24-5DE04B2F9173}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42151227-F7F7-4741-94D2-E5B4D4FE01E4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092EC725-5A16-43BC-90B7-65F9CB423854}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EB8F7F8-D19C-4D21-B903-3B84EA100776}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC3904F-6A92-47A9-8A1E-832BC7E71D72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B03EAD-5C55-4744-87F7-CFEBF1D873AC}"/>
 </file>